--- a/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
+++ b/main/ig/StructureDefinition-pdsm-comprehensive-provide-document-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T14:57:23+00:00</t>
+    <t>2026-10-13T09:06:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
